--- a/example/test.xlsx
+++ b/example/test.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b6eab892f612cd54/お勉強/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b6eab892f612cd54/お勉強/app/mock_exam/example/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{A94D9EFB-2FF5-4791-978C-B350696D70CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D59E2AF-782F-40D5-865B-CE88AFE94A8F}"/>
+  <xr:revisionPtr revIDLastSave="32" documentId="8_{A94D9EFB-2FF5-4791-978C-B350696D70CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C76AE1D1-72C3-4F8F-A425-26C657CE6F61}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0AC9D5F2-7A45-46E2-A200-CC009C944F57}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{0AC9D5F2-7A45-46E2-A200-CC009C944F57}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="19">
   <si>
     <t>category</t>
     <phoneticPr fontId="1"/>
@@ -61,18 +61,76 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>HTML5の要素のうち、開始タグと終了タグを省略できるものはどれか。すべて選びなさい</t>
-    <rPh sb="6" eb="8">
+    <t>1,2,4</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2,4</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>HTML5のDOCTIPE宣言として正しいものをすべて選べ</t>
+    <rPh sb="13" eb="15">
+      <t>センゲン</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>タダ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>エラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;!doctype html&gt;,&lt;!DOCTYPE HTML&gt;,&lt;! Doctype html&gt;,&lt;!doctype html &gt;,&lt; ! DOCTYPE HTML &gt;</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>HTML5のコメントとして正しくないものをすべて選べ</t>
+    <rPh sb="13" eb="14">
+      <t>タダ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>エラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;!-- コメント --&gt;,&lt;! -- コメント -- &gt;,&lt;!--- コメント ---&gt;,&lt;!-- ---コメント--- --&gt;,&lt;!-----コメント-----&gt;</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2,3,4,5</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>HTML5においてトランスペアレントの要素をすべて選べ</t>
+    <rPh sb="19" eb="21">
       <t>ヨウソ</t>
     </rPh>
-    <rPh sb="12" eb="14">
-      <t>カイシ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>シュウリョウ</t>
+    <rPh sb="25" eb="26">
+      <t>エラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>a,del,ruby,label,audio</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1,2,5</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>HTML5においてclassまたはidの指定方法で間違っているものをすべて選べ</t>
+    <rPh sb="20" eb="22">
+      <t>シテイ</t>
     </rPh>
     <rPh sb="22" eb="24">
-      <t>ショウリャク</t>
+      <t>ホウホウ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>マチガ</t>
     </rPh>
     <rPh sb="37" eb="38">
       <t>エラ</t>
@@ -80,26 +138,27 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>html,head,title,body,p</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>1,2,4</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>HTML5でエラーが発生するのはどれか</t>
-    <rPh sb="10" eb="12">
-      <t>ハッセイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>&lt;br&gt;,&lt;br/ &gt;,&lt;br /&gt;,&lt;br&gt;&lt;/br&gt;,&lt;br&gt;&lt;br /&gt;</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>2,4</t>
+    <t>class="",id="",class="abc xyz",id="abc xyz",class = "  abc    xyz"</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>hidden属性の指定方法として間違っているものをすべて選べ</t>
+    <rPh sb="6" eb="8">
+      <t>ゾクセイ</t>
+    </rPh>
+    <rPh sb="9" eb="13">
+      <t>シテイホウホウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>マチガ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>エラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;div hidden&gt; ~ &lt;/div&gt;,&lt;div hidden=""&gt; ~ &lt;/div&gt;,&lt;div hidden="true"&gt; ~ &lt;/div&gt;,&lt;div hidden=hidden&gt; ~ &lt;/div&gt;</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -152,7 +211,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -168,7 +227,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -484,13 +543,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC2BA737-CC34-4C1A-B793-FD9F665BD5EF}">
-  <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="84.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -504,32 +563,71 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>4</v>
       </c>
       <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" t="s">
-        <v>7</v>
-      </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/example/test.xlsx
+++ b/example/test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b6eab892f612cd54/お勉強/app/mock_exam/example/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="32" documentId="8_{A94D9EFB-2FF5-4791-978C-B350696D70CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C76AE1D1-72C3-4F8F-A425-26C657CE6F61}"/>
+  <xr:revisionPtr revIDLastSave="55" documentId="8_{A94D9EFB-2FF5-4791-978C-B350696D70CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4AE9770F-8765-4605-BF69-A5E5FFC260A9}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{0AC9D5F2-7A45-46E2-A200-CC009C944F57}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="31">
   <si>
     <t>category</t>
     <phoneticPr fontId="1"/>
@@ -159,6 +159,231 @@
   </si>
   <si>
     <t>&lt;div hidden&gt; ~ &lt;/div&gt;,&lt;div hidden=""&gt; ~ &lt;/div&gt;,&lt;div hidden="true"&gt; ~ &lt;/div&gt;,&lt;div hidden=hidden&gt; ~ &lt;/div&gt;</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>HTML5の属性のうち、任意の要素に指定可能でないものを1つ選べ</t>
+    <rPh sb="6" eb="8">
+      <t>ゾクセイ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ニンイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ヨウソ</t>
+    </rPh>
+    <rPh sb="18" eb="22">
+      <t>シテイカノウ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>エラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>dir,role,data,data-*,aria-*</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>HTML5に関する記述のうち、正しいものをすべて選べ</t>
+    <rPh sb="6" eb="7">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>キジュツ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>タダ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>エラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>base要素は0個または1個しか配置できない,title要素は0個または1個しか配置できない,base要素は必ず1個配置しなければならない,title要素は必ず1個配置しなければならない,base要素もtitle要素も指定できる数に制限はなく、最後の指定が有効になる</t>
+    <rPh sb="4" eb="6">
+      <t>ヨウソ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ハイチ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ヨウソ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>ハイチ</t>
+    </rPh>
+    <rPh sb="51" eb="53">
+      <t>ヨウソ</t>
+    </rPh>
+    <rPh sb="54" eb="55">
+      <t>カナラ</t>
+    </rPh>
+    <rPh sb="57" eb="58">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="58" eb="60">
+      <t>ハイチ</t>
+    </rPh>
+    <rPh sb="75" eb="77">
+      <t>ヨウソ</t>
+    </rPh>
+    <rPh sb="78" eb="79">
+      <t>カナラ</t>
+    </rPh>
+    <rPh sb="81" eb="84">
+      <t>コハイチ</t>
+    </rPh>
+    <rPh sb="98" eb="100">
+      <t>ヨウソ</t>
+    </rPh>
+    <rPh sb="106" eb="108">
+      <t>ヨウソ</t>
+    </rPh>
+    <rPh sb="109" eb="111">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="114" eb="115">
+      <t>カズ</t>
+    </rPh>
+    <rPh sb="116" eb="118">
+      <t>セイゲン</t>
+    </rPh>
+    <rPh sb="122" eb="124">
+      <t>サイゴ</t>
+    </rPh>
+    <rPh sb="125" eb="127">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="128" eb="130">
+      <t>ユウコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1,2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>navi,header,main,body,aside</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>以下の要素のうち、セクションを表す要素をすべて選べ</t>
+    <rPh sb="0" eb="2">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ヨウソ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>アラワ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ヨウソ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>エラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>以下の要素のうち、セクショニングルートに該当する要素をすべて選べ</t>
+    <rPh sb="0" eb="2">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ヨウソ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ガイトウ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ヨウソ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>エラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>table,body,iframe,figure,details</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2,4,5</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>address用のに入れるコンテンツとして適切なものをすべて選べ</t>
+    <rPh sb="7" eb="8">
+      <t>ヨウ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>テキセツ</t>
+    </rPh>
+    <rPh sb="30" eb="31">
+      <t>エラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>更新日時,免責事項,問い合わせ先,著作権に関する情報,問い合わせ先でない一般的な住所</t>
+    <rPh sb="0" eb="4">
+      <t>コウシンニチジ</t>
+    </rPh>
+    <rPh sb="5" eb="9">
+      <t>メンセキジコウ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>サキ</t>
+    </rPh>
+    <rPh sb="17" eb="20">
+      <t>チョサクケン</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>サキ</t>
+    </rPh>
+    <rPh sb="36" eb="39">
+      <t>イッパンテキ</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>ジュウショ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -543,10 +768,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC2BA737-CC34-4C1A-B793-FD9F665BD5EF}">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="2" max="2" width="84.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="55.5" customWidth="1"/>
+    <col min="3" max="3" width="221.4140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.55000000000000004">
@@ -629,6 +855,204 @@
       <c r="C6" t="s">
         <v>18</v>
       </c>
+      <c r="D6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" t="s">
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>

--- a/example/test.xlsx
+++ b/example/test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b6eab892f612cd54/お勉強/app/mock_exam/example/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="55" documentId="8_{A94D9EFB-2FF5-4791-978C-B350696D70CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4AE9770F-8765-4605-BF69-A5E5FFC260A9}"/>
+  <xr:revisionPtr revIDLastSave="98" documentId="8_{A94D9EFB-2FF5-4791-978C-B350696D70CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F08585E-2B6D-4866-AE48-B16124732256}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{0AC9D5F2-7A45-46E2-A200-CC009C944F57}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="49">
   <si>
     <t>category</t>
     <phoneticPr fontId="1"/>
@@ -104,37 +104,11 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>HTML5においてトランスペアレントの要素をすべて選べ</t>
-    <rPh sb="19" eb="21">
-      <t>ヨウソ</t>
-    </rPh>
-    <rPh sb="25" eb="26">
-      <t>エラ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>a,del,ruby,label,audio</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>1,2,5</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>HTML5においてclassまたはidの指定方法で間違っているものをすべて選べ</t>
-    <rPh sb="20" eb="22">
-      <t>シテイ</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>ホウホウ</t>
-    </rPh>
-    <rPh sb="25" eb="27">
-      <t>マチガ</t>
-    </rPh>
-    <rPh sb="37" eb="38">
-      <t>エラ</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -162,42 +136,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>HTML5の属性のうち、任意の要素に指定可能でないものを1つ選べ</t>
-    <rPh sb="6" eb="8">
-      <t>ゾクセイ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>ニンイ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>ヨウソ</t>
-    </rPh>
-    <rPh sb="18" eb="22">
-      <t>シテイカノウ</t>
-    </rPh>
-    <rPh sb="30" eb="31">
-      <t>エラ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>dir,role,data,data-*,aria-*</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>HTML5に関する記述のうち、正しいものをすべて選べ</t>
-    <rPh sb="6" eb="7">
-      <t>カン</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>キジュツ</t>
-    </rPh>
-    <rPh sb="15" eb="16">
-      <t>タダ</t>
-    </rPh>
-    <rPh sb="24" eb="25">
-      <t>エラ</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -384,6 +323,376 @@
     <rPh sb="40" eb="42">
       <t>ジュウショ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>記述のうち、正しいものをすべて選べ</t>
+    <rPh sb="0" eb="2">
+      <t>キジュツ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>タダ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>エラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>属性のうち、任意の要素に指定可能でないものを1つ選べ</t>
+    <rPh sb="0" eb="2">
+      <t>ゾクセイ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ニンイ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ヨウソ</t>
+    </rPh>
+    <rPh sb="12" eb="16">
+      <t>シテイカノウ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>エラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>classまたはidの指定方法で間違っているものをすべて選べ</t>
+    <rPh sb="11" eb="13">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ホウホウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>マチガ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>エラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>トランスペアレントの要素をすべて選べ</t>
+    <rPh sb="10" eb="12">
+      <t>ヨウソ</t>
+    </rPh>
+    <rPh sb="16" eb="17">
+      <t>エラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>em要素とstrong要素の違いについて述べた文章のうち正しいものを1つ選べ</t>
+    <rPh sb="2" eb="4">
+      <t>ヨウソ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ヨウソ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>チガ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ノ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ブンショウ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>タダ</t>
+    </rPh>
+    <rPh sb="36" eb="37">
+      <t>エラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>emもstrongも強調を示し、その度合いはstrongのほうが強い,emもstrongも重要性を示し、その度合いはstrongのほうが強い,emはタグをつける位置を変えると文章の意味も変化する,strongはタグをつける位置を変えると文章の意味も変化する,emもstrongもタグをつける位置で文章の意味が変わることはない</t>
+    <rPh sb="10" eb="12">
+      <t>キョウチョウ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>シメ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ドア</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>ツヨ</t>
+    </rPh>
+    <rPh sb="45" eb="48">
+      <t>ジュウヨウセイ</t>
+    </rPh>
+    <rPh sb="49" eb="50">
+      <t>シメ</t>
+    </rPh>
+    <rPh sb="54" eb="56">
+      <t>ドア</t>
+    </rPh>
+    <rPh sb="68" eb="69">
+      <t>ツヨ</t>
+    </rPh>
+    <rPh sb="80" eb="82">
+      <t>イチ</t>
+    </rPh>
+    <rPh sb="83" eb="84">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="87" eb="89">
+      <t>ブンショウ</t>
+    </rPh>
+    <rPh sb="90" eb="92">
+      <t>イミ</t>
+    </rPh>
+    <rPh sb="93" eb="95">
+      <t>ヘンカ</t>
+    </rPh>
+    <rPh sb="111" eb="113">
+      <t>イチ</t>
+    </rPh>
+    <rPh sb="114" eb="115">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="118" eb="120">
+      <t>ブンショウ</t>
+    </rPh>
+    <rPh sb="121" eb="123">
+      <t>イミ</t>
+    </rPh>
+    <rPh sb="124" eb="126">
+      <t>ヘンカ</t>
+    </rPh>
+    <rPh sb="145" eb="147">
+      <t>イチ</t>
+    </rPh>
+    <rPh sb="148" eb="150">
+      <t>ブンショウ</t>
+    </rPh>
+    <rPh sb="151" eb="153">
+      <t>イミ</t>
+    </rPh>
+    <rPh sb="154" eb="155">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Webページのフッターにあるcopyright情報はどの要素で入れるべきか1つ選べ</t>
+    <rPh sb="23" eb="25">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ヨウソ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="39" eb="40">
+      <t>エラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>div,small,aside,tfoot,address</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>timeの使い方で正しいものをすべて選べ</t>
+    <rPh sb="5" eb="6">
+      <t>ツカ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>タダ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>エラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>&lt;time&gt;17:45&lt;/time&gt;,&lt;time format="2017-11-28"&gt;当日&lt;/time&gt;の朝,&lt;time data="2017-11-28"&gt;当日&lt;/time&gt;の朝,&lt;time value="2017-11-28"&gt;当日&lt;/time&gt;の朝,&lt;time datatime="2017-11-28"&gt;当日&lt;/time&gt;の朝</t>
+    <rPh sb="45" eb="47">
+      <t>トウジツ</t>
+    </rPh>
+    <rPh sb="55" eb="56">
+      <t>アサ</t>
+    </rPh>
+    <rPh sb="81" eb="83">
+      <t>トウジツ</t>
+    </rPh>
+    <rPh sb="91" eb="92">
+      <t>アサ</t>
+    </rPh>
+    <rPh sb="118" eb="120">
+      <t>トウジツ</t>
+    </rPh>
+    <rPh sb="128" eb="129">
+      <t>アサ</t>
+    </rPh>
+    <rPh sb="158" eb="160">
+      <t>トウジツ</t>
+    </rPh>
+    <rPh sb="168" eb="169">
+      <t>アサ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1,5</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>レビュー記事における製品名、概要説明におけるキーワード、記事のリード文などをマークアップするのにふさわしい要素を1つ選べ</t>
+    <rPh sb="4" eb="6">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="10" eb="13">
+      <t>セイヒンメイ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ガイヨウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>キジ</t>
+    </rPh>
+    <rPh sb="34" eb="35">
+      <t>ブン</t>
+    </rPh>
+    <rPh sb="53" eb="55">
+      <t>ヨウソ</t>
+    </rPh>
+    <rPh sb="58" eb="59">
+      <t>エラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>b,i,s,u,q</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>学名をマークアップするのにふさわしい要素を1つ選べ</t>
+    <rPh sb="0" eb="2">
+      <t>ガクメイ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ヨウソ</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>エラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>I,u,q,b,s</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>すでに正しくなくなった部分や関係のない情報になった部分をマークアップするのにふさわしい要素を1つ選べ</t>
+    <rPh sb="3" eb="4">
+      <t>タダ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ブブン</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>カンケイ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ブブン</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>ヨウソ</t>
+    </rPh>
+    <rPh sb="48" eb="49">
+      <t>エラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>u,q,b,I,s</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>中国語の固有名詞やスペルミスをマークアップするのにふさわしい要素を1つ選べ</t>
+    <rPh sb="0" eb="3">
+      <t>チュウゴクゴ</t>
+    </rPh>
+    <rPh sb="4" eb="8">
+      <t>コユウメイシ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ヨウソ</t>
+    </rPh>
+    <rPh sb="35" eb="36">
+      <t>エラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>dlを用語の定義に使用する場合、dtの内部で使用すべき要素はどれか</t>
+    <rPh sb="3" eb="5">
+      <t>ヨウゴ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>テイギ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ナイブ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ヨウソ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>I,b,dd,dfn,cite</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>以下のルビ振りに関して、①②③にふさわしい組み合わせを1つ選べ  &lt;ruby&gt;&lt;①&gt;合格&lt;/①&gt;&lt;②&gt;(&lt;/②&gt;&lt;③&gt;ごうかく&lt;/③&gt;&lt;②&gt;)&lt;/②&gt;&lt;/ruby&gt;</t>
+    <rPh sb="0" eb="2">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>カン</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ク</t>
+    </rPh>
+    <rPh sb="23" eb="24">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>エラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>①rt②rb③rp,①rt②rp③rb,①rp②rt③rb,①rb②rp③rt,①rtc②rp③rt</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -768,7 +1077,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC2BA737-CC34-4C1A-B793-FD9F665BD5EF}">
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="55.5" customWidth="1"/>
@@ -822,13 +1131,13 @@
         <v>4</v>
       </c>
       <c r="B4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" t="s">
         <v>12</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>13</v>
-      </c>
-      <c r="D4" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.55000000000000004">
@@ -836,10 +1145,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D5" t="s">
         <v>6</v>
@@ -850,10 +1159,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D6">
         <v>3</v>
@@ -864,10 +1173,10 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D7">
         <v>3</v>
@@ -878,13 +1187,13 @@
         <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D8" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.55000000000000004">
@@ -892,10 +1201,10 @@
         <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D9">
         <v>5</v>
@@ -906,13 +1215,13 @@
         <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D10" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.55000000000000004">
@@ -920,10 +1229,10 @@
         <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C11" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D11">
         <v>3</v>
@@ -933,124 +1242,125 @@
       <c r="A12" t="s">
         <v>4</v>
       </c>
+      <c r="B12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12">
+        <v>3</v>
+      </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
         <v>4</v>
       </c>
+      <c r="B13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13">
+        <v>2</v>
+      </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
         <v>4</v>
       </c>
+      <c r="B14" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
         <v>4</v>
       </c>
+      <c r="B15" t="s">
+        <v>38</v>
+      </c>
+      <c r="C15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" t="s">
+        <v>41</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B17" t="s">
+        <v>42</v>
+      </c>
+      <c r="C17" t="s">
+        <v>43</v>
+      </c>
+      <c r="D17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B18" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18" t="s">
+        <v>41</v>
+      </c>
+      <c r="D18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="B19" t="s">
+        <v>45</v>
+      </c>
+      <c r="C19" t="s">
+        <v>46</v>
+      </c>
+      <c r="D19">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36" t="s">
+      <c r="B20" t="s">
+        <v>47</v>
+      </c>
+      <c r="C20" t="s">
+        <v>48</v>
+      </c>
+      <c r="D20">
         <v>4</v>
       </c>
     </row>
